--- a/product_order_forms/019_culinary_knife_sharpening_service_order_form--product_order_forms.xlsx
+++ b/product_order_forms/019_culinary_knife_sharpening_service_order_form--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -884,8 +884,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -913,12 +913,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'drop-off'}</t>
+          <t>drop-off</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Drop-Off'}</t>
+          <t>Drop-Off</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pick-up'}</t>
+          <t>pick-up</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pick-Up'}</t>
+          <t>Pick-Up</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sharpener'}</t>
+          <t>sharpener</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sharpener'}</t>
+          <t>Sharpener</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mobile_sharpening'}</t>
+          <t>mobile_sharpening</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mobile Sharpening'}</t>
+          <t>Mobile Sharpening</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'kitchen'}</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Kitchen'}</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
